--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38674,7 +38674,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39406,7 +39406,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40687,7 +40687,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40809,7 +40809,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41541,7 +41541,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42212,7 +42212,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42334,7 +42334,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42578,7 +42578,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43066,7 +43066,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43310,7 +43310,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43493,7 +43493,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43920,7 +43920,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43981,7 +43981,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44103,7 +44103,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44164,7 +44164,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44225,7 +44225,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44408,7 +44408,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44469,7 +44469,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44530,7 +44530,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44591,7 +44591,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44713,7 +44713,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44896,7 +44896,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44957,7 +44957,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45079,7 +45079,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45201,7 +45201,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45262,7 +45262,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45323,7 +45323,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45445,7 +45445,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45567,7 +45567,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45689,7 +45689,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45750,7 +45750,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45811,7 +45811,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -45994,7 +45994,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46055,7 +46055,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46116,7 +46116,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46238,7 +46238,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46604,7 +46604,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46726,7 +46726,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46909,7 +46909,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46970,7 +46970,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47092,7 +47092,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47214,7 +47214,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47275,7 +47275,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47336,7 +47336,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47458,7 +47458,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47580,7 +47580,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47702,7 +47702,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47824,7 +47824,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -47946,7 +47946,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48068,7 +48068,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48251,7 +48251,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48312,7 +48312,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48373,7 +48373,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -48434,7 +48434,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -48495,7 +48495,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48617,7 +48617,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48739,7 +48739,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -48800,7 +48800,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -48861,7 +48861,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -48922,7 +48922,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -48983,7 +48983,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49044,7 +49044,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49105,7 +49105,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49166,7 +49166,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -49227,7 +49227,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49288,7 +49288,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -49349,7 +49349,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49410,7 +49410,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -49471,7 +49471,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -49532,7 +49532,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49593,7 +49593,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49654,7 +49654,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -49776,7 +49776,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -49898,7 +49898,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -49959,7 +49959,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50020,7 +50020,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50081,7 +50081,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -50142,7 +50142,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50203,7 +50203,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -50264,7 +50264,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -50325,7 +50325,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2598,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2854,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3041,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3106,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3366,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3496,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3626,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3882,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4134,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4199,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4451,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4516,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4581,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4833,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4959,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5024,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5089,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5215,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5528,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5849,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6536,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6723,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6788,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6853,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6979,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7044,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7170,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7605,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7670,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7796,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7861,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8174,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8369,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8800,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8930,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8995,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9060,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9125,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9434,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9621,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9747,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9812,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9938,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10125,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10190,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10255,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10320,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10446,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10511,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10576,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10641,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10771,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10836,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11023,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11397,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11523,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11588,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11775,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11840,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12153,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12584,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12649,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12714,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12840,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12966,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13096,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13161,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13287,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13352,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13417,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13482,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13608,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13921,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14169,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14364,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14429,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14559,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14624,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14689,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14754,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14941,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15006,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15132,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15197,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15262,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15579,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15644,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15774,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15904,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16095,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16347,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16534,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16599,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17099,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17538,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17603,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17794,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17859,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17924,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17989,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18180,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18997,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19184,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19249,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19375,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19684,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19749,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20070,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20383,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20448,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20513,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20826,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21765,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21830,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22208,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22395,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22521,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22834,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23204,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23334,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23590,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23781,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23846,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24159,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24732,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24797,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24862,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24988,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25240,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25553,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25618,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25809,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26000,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26065,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26130,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26260,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26451,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26638,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +26886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27081,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27146,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27337,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27658,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27845,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28040,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28170,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28422,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28735,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28800,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29052,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29682,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29747,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29877,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +29942,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30129,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30255,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30320,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30515,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30641,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30767,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31015,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31080,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31145,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31210,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31966,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32031,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32096,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32161,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32352,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32417,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32482,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32677,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +32742,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33055,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33307,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33433,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33498,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33563,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33628,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33693,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33758,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34518,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34583,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34648,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34713,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34839,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +34904,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35030,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35095,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35286,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35351,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35599,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35725,11 @@
           <t>77.550.346-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +35977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36042,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36485,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36550,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36615,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +36680,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36745,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +36875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +36940,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37192,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37387,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37452,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37578,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +37708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37773,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37838,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38025,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38151,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38407,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +38915,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39041,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39106,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39232,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39297,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39553,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39618,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +39683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +39809,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +39874,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40183,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40248,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40313,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +40378,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +40443,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +40508,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +40573,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +40699,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +40886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +41077,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41272,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +41467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +41532,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41597,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +41662,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +41727,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +41792,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +41857,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +41983,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42109,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42174,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42239,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +42369,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +42564,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +42629,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +42694,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +42759,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +43129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43255,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43381,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43507,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41920,7 +43572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41981,7 +43637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42225,7 +43885,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44072,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +44259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42652,7 +44324,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +44389,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +44515,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42896,7 +44580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43079,7 +44767,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43262,7 +44954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43323,7 +45019,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43384,7 +45084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +45271,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43628,7 +45336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43750,7 +45462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43811,7 +45527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +45653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +45779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44177,7 +45905,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44238,7 +45970,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44360,7 +46096,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +46161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44482,7 +46226,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44787,7 +46535,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44848,7 +46600,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44909,7 +46665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45031,7 +46791,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45214,7 +46978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45397,7 +47165,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45458,7 +47230,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45519,7 +47295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45580,7 +47360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45763,7 +47547,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45885,7 +47673,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45946,7 +47738,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46007,7 +47803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46068,7 +47868,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46373,7 +48177,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +48364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46617,7 +48429,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46800,7 +48616,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +48803,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47044,7 +48868,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47166,7 +48994,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47227,7 +49059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47288,7 +49124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +49189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47410,7 +49254,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +49319,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47532,7 +49384,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47593,7 +49449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47654,7 +49514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47776,7 +49640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47837,7 +49705,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48142,7 +50014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48264,7 +50140,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48325,7 +50205,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48386,7 +50270,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48630,7 +50518,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48691,7 +50583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48813,7 +50709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48874,7 +50774,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48935,7 +50839,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48996,7 +50904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49118,7 +51030,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49240,7 +51156,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49301,7 +51221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49362,7 +51286,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49667,7 +51595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49850,7 +51782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49972,7 +51908,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50033,7 +51973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50094,7 +52038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50155,7 +52103,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2025.xlsx
@@ -749,7 +749,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1712,7 +1716,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2098,7 +2106,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2663,7 +2675,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2919,7 +2935,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2980,7 +3000,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3691,7 +3715,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4390,7 +4418,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4711,7 +4743,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4898,7 +4934,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5280,7 +5320,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5341,7 +5385,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5658,7 +5706,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6040,7 +6092,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6227,7 +6283,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6475,7 +6535,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6726,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7235,7 +7303,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7483,7 +7555,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8113,7 +8189,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8434,7 +8514,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8617,7 +8701,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8739,7 +8827,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9190,7 +9282,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10064,7 +10160,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11653,7 +11753,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11714,7 +11818,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11905,7 +12013,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12027,7 +12139,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12218,7 +12334,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12401,7 +12521,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12462,7 +12586,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13795,7 +13923,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14118,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17355,7 +17491,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18936,7 +19076,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19501,7 +19645,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20643,7 +20791,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20891,7 +21043,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21017,7 +21173,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21704,7 +21864,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21895,7 +22059,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22273,7 +22441,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22586,7 +22758,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22960,7 +23136,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23976,7 +24156,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24224,7 +24408,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25179,7 +25367,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25366,7 +25558,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25492,7 +25688,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26703,7 +26903,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27211,7 +27415,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28548,7 +28756,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28991,7 +29203,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29117,7 +29333,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29556,7 +29776,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30068,7 +30292,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30832,7 +31060,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31844,7 +32076,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32291,7 +32527,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32933,7 +33173,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33120,7 +33364,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33372,7 +33620,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33888,7 +34140,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35225,7 +35481,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35416,7 +35676,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35664,7 +35928,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36172,7 +36440,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36298,7 +36570,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37964,7 +38240,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38216,7 +38496,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38602,7 +38886,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38728,7 +39016,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38854,7 +39146,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39748,7 +40044,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40638,7 +40938,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40825,7 +41129,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40951,7 +41259,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41922,7 +42234,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42048,7 +42364,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42885,7 +43205,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43194,7 +43518,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43763,7 +44091,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44893,7 +45225,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45210,7 +45546,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45592,7 +45932,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46352,7 +46696,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46917,7 +47265,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47043,7 +47395,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48242,7 +48598,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48933,7 +49293,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49953,7 +50317,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50079,7 +50447,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50457,7 +50829,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51412,7 +51788,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51534,7 +51914,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51847,7 +52231,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52229,7 +52617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
